--- a/ValueSet-onc-relational-findings-vs.xlsx
+++ b/ValueSet-onc-relational-findings-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-relational-findings-vs.xlsx
+++ b/ValueSet-onc-relational-findings-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-relational-findings-vs.xlsx
+++ b/ValueSet-onc-relational-findings-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-relational-findings-vs.xlsx
+++ b/ValueSet-onc-relational-findings-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
